--- a/docs/examples/Project_Finance_Economic_Review_CP020.xlsx
+++ b/docs/examples/Project_Finance_Economic_Review_CP020.xlsx
@@ -11,11 +11,75 @@
     <sheet name="Milestones" sheetId="7" r:id="rId7"/>
     <sheet name="Alerts" sheetId="8" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Summary'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Labor'!$A$1:$Q$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Labor'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Expenses'!$A$1:$P$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Expenses'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Unbilled WIP'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Unbilled WIP'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Daily minimum'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Daily minimum'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Invoices'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Invoices'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Milestones'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Milestones'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Alerts'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Alerts'!$1:$1</definedName>
+  </definedNames>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red]-#,##0.00"/>
+  </numFmts>
+  <fonts count="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+  </fonts>
+  <fills count="1">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+  </cellXfs>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1" style="2"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -30,10 +94,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>displayValue</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>exactMinorUnits</t>
         </is>
@@ -60,6 +139,21 @@
           <t/>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -82,6 +176,21 @@
           <t/>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -104,6 +213,21 @@
           <t/>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -126,6 +250,21 @@
           <t/>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -148,6 +287,21 @@
           <t/>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -170,6 +324,21 @@
           <t/>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -192,6 +361,21 @@
           <t/>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -214,6 +398,21 @@
           <t/>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -236,6 +435,21 @@
           <t/>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -258,6 +472,21 @@
           <t/>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -280,6 +509,21 @@
           <t/>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -302,6 +546,21 @@
           <t/>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -324,6 +583,21 @@
           <t/>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -346,6 +620,21 @@
           <t/>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -368,6 +657,21 @@
           <t/>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -390,6 +694,21 @@
           <t/>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -407,7 +726,20 @@
           <t>$44,070.25</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18">
+        <v>44070.25</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>4407025</t>
         </is>
@@ -434,6 +766,21 @@
           <t/>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -451,7 +798,20 @@
           <t>$26,730.31</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20">
+        <v>26730.31</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>2673031</t>
         </is>
@@ -478,6 +838,19 @@
           <t/>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F21">
+        <v>37.75</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -500,6 +873,21 @@
           <t/>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -522,6 +910,21 @@
           <t/>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -544,6 +947,21 @@
           <t/>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -566,6 +984,21 @@
           <t/>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -588,6 +1021,21 @@
           <t/>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -605,7 +1053,20 @@
           <t>$25,000.00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27">
+        <v>25000</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>2500000</t>
         </is>
@@ -627,7 +1088,20 @@
           <t>$45,800.56</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28">
+        <v>45800.56</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>4580056</t>
         </is>
@@ -654,6 +1128,21 @@
           <t/>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -676,6 +1165,21 @@
           <t/>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -698,6 +1202,21 @@
           <t/>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -720,6 +1239,21 @@
           <t/>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -734,10 +1268,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t/>
         </is>
       </c>
       <c r="D33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -764,6 +1313,21 @@
           <t/>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -786,6 +1350,21 @@
           <t/>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -808,6 +1387,21 @@
           <t/>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -830,6 +1424,21 @@
           <t/>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -852,6 +1461,21 @@
           <t/>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -874,13 +1498,50 @@
           <t/>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G39"/>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1" style="2"/>
+    <col min="9" max="9" width="14" customWidth="1" style="2"/>
+    <col min="10" max="10" width="20" customWidth="1" style="2"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="25" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="30" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -985,15 +1646,11 @@
           <t>work</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>131.50</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>7890</t>
-        </is>
+      <c r="D2">
+        <v>131.5</v>
+      </c>
+      <c r="E2">
+        <v>7890</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1007,17 +1664,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1072,15 +1729,11 @@
           <t>work</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>134.60</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>8076</t>
-        </is>
+      <c r="D3">
+        <v>134.6</v>
+      </c>
+      <c r="E3">
+        <v>8076</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1094,17 +1747,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1159,15 +1812,11 @@
           <t>work</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>129.50</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>7770</t>
-        </is>
+      <c r="D4">
+        <v>129.5</v>
+      </c>
+      <c r="E4">
+        <v>7770</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1181,17 +1830,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1246,15 +1895,11 @@
           <t>work</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>148.00</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>8880</t>
-        </is>
+      <c r="D5">
+        <v>148</v>
+      </c>
+      <c r="E5">
+        <v>8880</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1268,17 +1913,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1318,11 +1963,32 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q5"/>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1" style="2"/>
+    <col min="7" max="7" width="12" customWidth="1" style="2"/>
+    <col min="8" max="8" width="10" customWidth="1" style="2"/>
+    <col min="9" max="9" width="23" customWidth="1" style="2"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="19" customWidth="1"/>
+    <col min="16" max="16" width="33" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1392,7 +2058,17 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>actualCostExactMinor</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>revenueExactMinor</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pendingFinanceRevenueExactMinor</t>
         </is>
       </c>
     </row>
@@ -1424,22 +2100,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1463,6 +2139,16 @@
         </is>
       </c>
       <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1496,22 +2182,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t/>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1539,13 +2225,34 @@
           <t/>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P3"/>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1" style="2"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1580,11 +2287,22 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1"/>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1" style="2"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1619,11 +2337,28 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1"/>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1" style="2"/>
+    <col min="8" max="8" width="11" customWidth="1" style="2"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="21" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1688,11 +2423,21 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L1"/>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1" style="2"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1722,11 +2467,18 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E1"/>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1741,5 +2493,8 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B1"/>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>